--- a/models/(Gabriela_Mangrove) restoration_Mangrove_Seed_Dispersal_2026-06-16-00-05-14._GABRIELA SARMIENTOxlsx.xlsx
+++ b/models/(Gabriela_Mangrove) restoration_Mangrove_Seed_Dispersal_2026-06-16-00-05-14._GABRIELA SARMIENTOxlsx.xlsx
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11890</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>35</v>
